--- a/data/Resultados.xlsx
+++ b/data/Resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\Spartans\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32727CEB-E16E-43B1-A569-AE2401A9C8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D2DA5D-AE04-4905-8CF2-B15198FD9ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{F1D52910-ECB9-4C99-A3C7-3719A8882D54}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="68">
   <si>
     <t>Fecha</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>Pita</t>
+  </si>
+  <si>
+    <t>Coto,Marcos,Marcos</t>
   </si>
 </sst>
 </file>
@@ -2964,6 +2967,7 @@
   <cols>
     <col min="2" max="2" width="19.6640625" style="32" customWidth="1"/>
     <col min="6" max="6" width="18.77734375" style="32" customWidth="1"/>
+    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -3077,7 +3081,9 @@
       <c r="F5" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="43"/>
+      <c r="G5" s="43" t="s">
+        <v>67</v>
+      </c>
       <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">

--- a/data/Resultados.xlsx
+++ b/data/Resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\Spartans\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D2DA5D-AE04-4905-8CF2-B15198FD9ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCE9D87-2EFA-4116-9AF8-951C447B7D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{F1D52910-ECB9-4C99-A3C7-3719A8882D54}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="69">
   <si>
     <t>Fecha</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>Coto,Marcos,Marcos</t>
+  </si>
+  <si>
+    <t>Coto</t>
   </si>
 </sst>
 </file>
@@ -3084,7 +3087,9 @@
       <c r="G5" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="44" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">

--- a/data/Resultados.xlsx
+++ b/data/Resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\Spartans\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCE9D87-2EFA-4116-9AF8-951C447B7D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7723BA56-5F40-4652-95C1-54514CF95FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{F1D52910-ECB9-4C99-A3C7-3719A8882D54}"/>
   </bookViews>
@@ -1704,11 +1704,15 @@
       <c r="B9" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C9" s="13">
+        <v>0</v>
+      </c>
       <c r="D9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="13"/>
+      <c r="E9" s="13">
+        <v>3</v>
+      </c>
       <c r="F9" s="14" t="s">
         <v>22</v>
       </c>
@@ -1722,11 +1726,15 @@
       <c r="B10" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
       <c r="F10" s="15" t="s">
         <v>32</v>
       </c>
@@ -1740,11 +1748,15 @@
       <c r="B11" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
       <c r="D11" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
       <c r="F11" s="15" t="s">
         <v>26</v>
       </c>
@@ -1758,11 +1770,15 @@
       <c r="B12" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3">
+        <v>7</v>
+      </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
       <c r="F12" s="15" t="s">
         <v>28</v>
       </c>
@@ -1776,11 +1792,15 @@
       <c r="B13" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
       <c r="D13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
       <c r="F13" s="15" t="s">
         <v>30</v>
       </c>
@@ -3184,11 +3204,15 @@
       <c r="B10" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="52"/>
+      <c r="C10" s="52">
+        <v>3</v>
+      </c>
       <c r="D10" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="53"/>
+      <c r="E10" s="53">
+        <v>0</v>
+      </c>
       <c r="F10" s="54" t="s">
         <v>8</v>
       </c>
@@ -3202,11 +3226,15 @@
       <c r="B11" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="34">
+        <v>1</v>
+      </c>
       <c r="D11" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="35"/>
+      <c r="E11" s="35">
+        <v>3</v>
+      </c>
       <c r="F11" s="56" t="s">
         <v>54</v>
       </c>
@@ -3220,11 +3248,15 @@
       <c r="B12" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="34">
+        <v>0</v>
+      </c>
       <c r="D12" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="35">
+        <v>1</v>
+      </c>
       <c r="F12" s="56" t="s">
         <v>30</v>
       </c>
@@ -3238,11 +3270,15 @@
       <c r="B13" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="34">
+        <v>0</v>
+      </c>
       <c r="D13" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="35">
+        <v>3</v>
+      </c>
       <c r="F13" s="56" t="s">
         <v>56</v>
       </c>
@@ -3256,11 +3292,15 @@
       <c r="B14" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="34">
+        <v>1</v>
+      </c>
       <c r="D14" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="35"/>
+      <c r="E14" s="35">
+        <v>3</v>
+      </c>
       <c r="F14" s="56" t="s">
         <v>58</v>
       </c>
@@ -3274,11 +3314,15 @@
       <c r="B15" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="34">
+        <v>4</v>
+      </c>
       <c r="D15" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="35">
+        <v>1</v>
+      </c>
       <c r="F15" s="56" t="s">
         <v>28</v>
       </c>
@@ -3292,11 +3336,15 @@
       <c r="B16" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="58">
+        <v>2</v>
+      </c>
       <c r="D16" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59"/>
+      <c r="E16" s="59">
+        <v>2</v>
+      </c>
       <c r="F16" s="60" t="s">
         <v>60</v>
       </c>

--- a/data/Resultados.xlsx
+++ b/data/Resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\Spartans\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F34E1E-9290-4D2E-A9A5-CFE28506D632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7E270B-9D8E-4444-ADD4-B873B8745F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{F1D52910-ECB9-4C99-A3C7-3719A8882D54}"/>
   </bookViews>
@@ -5937,7 +5937,7 @@
         <v>3</v>
       </c>
       <c r="E63" s="24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F63" s="45" t="s">
         <v>54</v>
@@ -8438,7 +8438,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="44">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -8453,7 +8453,7 @@
       <c r="A4" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="44">
         <v>3</v>
       </c>
     </row>

--- a/data/Resultados.xlsx
+++ b/data/Resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\Spartans\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7E270B-9D8E-4444-ADD4-B873B8745F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9E831D-61D1-4887-83C4-4016EB654341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{F1D52910-ECB9-4C99-A3C7-3719A8882D54}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{F1D52910-ECB9-4C99-A3C7-3719A8882D54}"/>
   </bookViews>
   <sheets>
     <sheet name="Serie 35" sheetId="1" r:id="rId1"/>
@@ -8422,7 +8422,7 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8438,7 +8438,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="44">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">

--- a/data/Resultados.xlsx
+++ b/data/Resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\Spartans\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9E831D-61D1-4887-83C4-4016EB654341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B940FBEB-21C5-4176-9098-65741211E923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{F1D52910-ECB9-4C99-A3C7-3719A8882D54}"/>
   </bookViews>
@@ -8438,7 +8438,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="44">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
